--- a/temp_excel_files/CBL Sanlam.xlsx
+++ b/temp_excel_files/CBL Sanlam.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29318"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://citybrokersltdmu.sharepoint.com/sites/Accounts/Shared Documents/INSURERS/STATEMENTS &amp; RECONS/2024-2025/Reconciliation 30.06.2025/FRCI/Sanlam/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E5EB16B-0B24-42F1-B3EA-5DAA704786C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{5E5EB16B-0B24-42F1-B3EA-5DAA704786C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01587AAF-2AC3-4E14-BFA4-31B1736F705C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39803825-11C7-4E50-BAEF-7F882B139340}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -104,24 +104,24 @@
     <t>SANLAM GENERAL INSURANCE LTD</t>
   </si>
   <si>
+    <t>POL-DEF-Feb-23-1001</t>
+  </si>
+  <si>
+    <t>KI SIGNATURE VILLAS LTD &amp;/OR SUBSEQUENT OWNERS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>MUR</t>
   </si>
   <si>
-    <t/>
+    <t>31-01-2024 to 31-01-2034</t>
   </si>
   <si>
     <t>DEFECTS INSURANCE</t>
   </si>
   <si>
-    <t>POL-DEF-Feb-23-1001</t>
-  </si>
-  <si>
-    <t>KI SIGNATURE VILLAS LTD &amp;/OR SUBSEQUENT OWNERS</t>
-  </si>
-  <si>
-    <t>31-01-2024 to 31-01-2034</t>
-  </si>
-  <si>
     <t>POL-DEF-May-23-1012</t>
   </si>
   <si>
@@ -143,229 +143,229 @@
     <t>01-01-2025 to 01-01-2035</t>
   </si>
   <si>
+    <t>POL-CAR-TPL-Jul-23-1052</t>
+  </si>
+  <si>
+    <t>TAMARIN SAVANNAH LTD &amp;/OR CONTRACTORS &amp;/OR SUB CONTRACTORS</t>
+  </si>
+  <si>
+    <t>PY52706012023000023</t>
+  </si>
+  <si>
+    <t>01-03-2024 to 01-09-2025</t>
+  </si>
+  <si>
+    <t>CAR &amp; TPL</t>
+  </si>
+  <si>
+    <t>POL-DEF-Jul-23-1022</t>
+  </si>
+  <si>
+    <t>TAMARIN SAVANNAH LTD &amp;/OR SUBSEQUENT OWNERS</t>
+  </si>
+  <si>
+    <t>01-04-2025 to 01-04-2035</t>
+  </si>
+  <si>
+    <t>POL-DEF-Jul-23-1023</t>
+  </si>
+  <si>
+    <t>POL-DEF-Jul-23-1024</t>
+  </si>
+  <si>
+    <t>01-09-2025 to 01-09-2035</t>
+  </si>
+  <si>
+    <t>POL-DEF-Oct-23-1025</t>
+  </si>
+  <si>
+    <t>WESTBYMJ LTD &amp;/OR SUBSEQUENT OWNERS,</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>01-07-2024 to 01-07-2034</t>
+  </si>
+  <si>
+    <t>POL-DEF-Oct-23-1026</t>
+  </si>
+  <si>
+    <t>01-01-2026 to 01-01-2036</t>
+  </si>
+  <si>
+    <t>POL-DEF-Oct-23-1027</t>
+  </si>
+  <si>
+    <t>04-12-2024 to 04-12-2034</t>
+  </si>
+  <si>
+    <t>POL-DEF-May-24-1006</t>
+  </si>
+  <si>
+    <t>01-10-2025 to 01-10-2035</t>
+  </si>
+  <si>
+    <t>POL-DEF-Jun-24-1007</t>
+  </si>
+  <si>
+    <t>FRENCH TOUCH LTD &amp;/OR SUBSEQUENT OWNERS</t>
+  </si>
+  <si>
+    <t>06-02-2024 to 06-02-2034</t>
+  </si>
+  <si>
+    <t>POL-DEF-Jun-24-1009</t>
+  </si>
+  <si>
+    <t>SEKOYA17 LTD &amp;/OR MNJ PROPERTIES LTD &amp;/OR SUBSEQUENT OWNERS</t>
+  </si>
+  <si>
+    <t>POL-MH+TPL-Dec-19-1397\R4</t>
+  </si>
+  <si>
+    <t>NAIRAC ROBERT EDOUARD LAURENCE MR</t>
+  </si>
+  <si>
+    <t>PY527080320234000029</t>
+  </si>
+  <si>
+    <t>01-11-2024 to 01-11-2025</t>
+  </si>
+  <si>
     <t>MARINE HULL &amp; TPL</t>
   </si>
   <si>
-    <t>POL-CAR-TPL-Jul-23-1052</t>
-  </si>
-  <si>
-    <t>TAMARIN SAVANNAH LTD &amp;/OR CONTRACTORS &amp;/OR SUB CONTRACTORS</t>
-  </si>
-  <si>
-    <t>PY52706012023000023</t>
-  </si>
-  <si>
-    <t>01-03-2024 to 01-09-2025</t>
-  </si>
-  <si>
-    <t>CAR &amp; TPL</t>
-  </si>
-  <si>
-    <t>POL-DEF-Jul-23-1022</t>
-  </si>
-  <si>
-    <t>TAMARIN SAVANNAH LTD &amp;/OR SUBSEQUENT OWNERS</t>
-  </si>
-  <si>
-    <t>01-04-2025 to 01-04-2035</t>
-  </si>
-  <si>
-    <t>POL-DEF-Jul-23-1023</t>
-  </si>
-  <si>
-    <t>POL-DEF-Jul-23-1024</t>
-  </si>
-  <si>
-    <t>01-09-2025 to 01-09-2035</t>
+    <t>POL-DEF-Nov-24-1016</t>
+  </si>
+  <si>
+    <t>DIL PROPERTY DEVELOPMENT LTD &amp;/OR SUBSEQUENT OWNERS</t>
+  </si>
+  <si>
+    <t>DN52706092024000012</t>
+  </si>
+  <si>
+    <t>01-03-2026 to 01-03-2036</t>
+  </si>
+  <si>
+    <t>POL-CAR-TPL-May-23-1025</t>
+  </si>
+  <si>
+    <t>POL-CAR-TPL-May-23-1025\E1</t>
+  </si>
+  <si>
+    <t>FAIRY WEST CO LTD &amp;/OR BLUE GREEN SIGNATURE CO LTD &amp;/OR CONTRACTORS &amp;/OR SUB-CONTRACTORS</t>
+  </si>
+  <si>
+    <t>DN52706012025000003</t>
+  </si>
+  <si>
+    <t>01-12-2024 to 01-10-2025</t>
+  </si>
+  <si>
+    <t>POL-CAR-TPL-Dec-24-73</t>
+  </si>
+  <si>
+    <t>MONDO PROPERTIES LTD &amp;/OR AMARE17.1 LTD &amp;/OR CONTRACTORS &amp;/OR OTHER SUB-CONTRACTORS</t>
+  </si>
+  <si>
+    <t>PY52706012025000002</t>
+  </si>
+  <si>
+    <t>27-10-2024 to 26-10-2026</t>
+  </si>
+  <si>
+    <t>POL-DEF-Dec-24-1017</t>
+  </si>
+  <si>
+    <t>AMARE17.1  LTD &amp;/OR MNJ PROPERTIES LTD &amp;/OR SUBSEQUENT OWNERS</t>
+  </si>
+  <si>
+    <t>PY52706092025000002</t>
+  </si>
+  <si>
+    <t>27-10-2026 to 26-10-2036</t>
+  </si>
+  <si>
+    <t>POL-F&amp;A-Mar-25-13</t>
+  </si>
+  <si>
+    <t>TAMARIN SAVANNAH LTD</t>
+  </si>
+  <si>
+    <t>PY5274012025000001</t>
+  </si>
+  <si>
+    <t>03-03-2025 to 01-03-2026</t>
+  </si>
+  <si>
+    <t>FIRE &amp; ALLIED PERILS</t>
+  </si>
+  <si>
+    <t>POL-PL-Mar-25-14</t>
+  </si>
+  <si>
+    <t>PY52702032025000001</t>
+  </si>
+  <si>
+    <t>PUBLIC LIABILITY</t>
+  </si>
+  <si>
+    <t>POL-TPL-May-24-4</t>
+  </si>
+  <si>
+    <t>POL-TPL-May-24-4\E1</t>
+  </si>
+  <si>
+    <t>MARGEOT NICHOLAS GERARD MR</t>
+  </si>
+  <si>
+    <t>PY5270803202000010</t>
+  </si>
+  <si>
+    <t>12-03-2025 to 01-06-2025</t>
+  </si>
+  <si>
+    <t>MARINE THIRD PARTY LIABILITY</t>
+  </si>
+  <si>
+    <t>POL-DEF-Mar-25-1011</t>
+  </si>
+  <si>
+    <t>CREATIVE PROPERTIES LTD &amp;/OR SUBSEQUENT OWNERS</t>
+  </si>
+  <si>
+    <t>15-01-2026 to 14-01-2036</t>
+  </si>
+  <si>
+    <t>POL-CAR-TPL-Jul-23-1050</t>
+  </si>
+  <si>
+    <t>POL-CAR-TPL-Jul-23-1050\E1</t>
+  </si>
+  <si>
+    <t>DN52706012025000015</t>
+  </si>
+  <si>
+    <t>01-04-2025 to 31-03-2026</t>
+  </si>
+  <si>
+    <t>POL-CAR-TPL-Sep-23-1059</t>
+  </si>
+  <si>
+    <t>POL-CAR-TPL-Sep-23-1059\E2</t>
   </si>
   <si>
     <t>TAYELAMAY &amp; SONS ENTERPRISE LTD &amp;/OR NEW SOCIAL LIVING DEVELOPMENT LTD &amp;/OR SUB CONTRACTORS FOR THEIR RESPECTIVE RIGHTS AND INTERESTS</t>
   </si>
   <si>
-    <t>POL-CAR-TPL-Sep-23-1059</t>
-  </si>
-  <si>
     <t>PY52706012023000013</t>
   </si>
   <si>
+    <t>31-05-2025 to 31-08-2025</t>
+  </si>
+  <si>
     <t>POL-CAR-TPL-Sep-23-1060</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>POL-DEF-Oct-23-1025</t>
-  </si>
-  <si>
-    <t>WESTBYMJ LTD &amp;/OR SUBSEQUENT OWNERS,</t>
-  </si>
-  <si>
-    <t>01-07-2024 to 01-07-2034</t>
-  </si>
-  <si>
-    <t>POL-DEF-Oct-23-1026</t>
-  </si>
-  <si>
-    <t>01-01-2026 to 01-01-2036</t>
-  </si>
-  <si>
-    <t>POL-DEF-Oct-23-1027</t>
-  </si>
-  <si>
-    <t>04-12-2024 to 04-12-2034</t>
-  </si>
-  <si>
-    <t>POL-DEF-May-24-1006</t>
-  </si>
-  <si>
-    <t>01-10-2025 to 01-10-2035</t>
-  </si>
-  <si>
-    <t>POL-DEF-Jun-24-1007</t>
-  </si>
-  <si>
-    <t>FRENCH TOUCH LTD &amp;/OR SUBSEQUENT OWNERS</t>
-  </si>
-  <si>
-    <t>06-02-2024 to 06-02-2034</t>
-  </si>
-  <si>
-    <t>POL-DEF-Jun-24-1009</t>
-  </si>
-  <si>
-    <t>SEKOYA17 LTD &amp;/OR MNJ PROPERTIES LTD &amp;/OR SUBSEQUENT OWNERS</t>
-  </si>
-  <si>
-    <t>POL-MH+TPL-Dec-19-1397\R4</t>
-  </si>
-  <si>
-    <t>NAIRAC ROBERT EDOUARD LAURENCE MR</t>
-  </si>
-  <si>
-    <t>PY527080320234000029</t>
-  </si>
-  <si>
-    <t>01-11-2024 to 01-11-2025</t>
-  </si>
-  <si>
-    <t>FIRE &amp; ALLIED PERILS</t>
-  </si>
-  <si>
-    <t>POL-DEF-Nov-24-1016</t>
-  </si>
-  <si>
-    <t>DIL PROPERTY DEVELOPMENT LTD &amp;/OR SUBSEQUENT OWNERS</t>
-  </si>
-  <si>
-    <t>DN52706092024000012</t>
-  </si>
-  <si>
-    <t>01-03-2026 to 01-03-2036</t>
-  </si>
-  <si>
-    <t>POL-CAR-TPL-May-23-1025</t>
-  </si>
-  <si>
-    <t>POL-CAR-TPL-May-23-1025\E1</t>
-  </si>
-  <si>
-    <t>FAIRY WEST CO LTD &amp;/OR BLUE GREEN SIGNATURE CO LTD &amp;/OR CONTRACTORS &amp;/OR SUB-CONTRACTORS</t>
-  </si>
-  <si>
-    <t>DN52706012025000003</t>
-  </si>
-  <si>
-    <t>01-12-2024 to 01-10-2025</t>
-  </si>
-  <si>
-    <t>POL-CAR-TPL-Dec-24-73</t>
-  </si>
-  <si>
-    <t>MONDO PROPERTIES LTD &amp;/OR AMARE17.1 LTD &amp;/OR CONTRACTORS &amp;/OR OTHER SUB-CONTRACTORS</t>
-  </si>
-  <si>
-    <t>PY52706012025000002</t>
-  </si>
-  <si>
-    <t>27-10-2024 to 26-10-2026</t>
-  </si>
-  <si>
-    <t>POL-DEF-Dec-24-1017</t>
-  </si>
-  <si>
-    <t>AMARE17.1  LTD &amp;/OR MNJ PROPERTIES LTD &amp;/OR SUBSEQUENT OWNERS</t>
-  </si>
-  <si>
-    <t>PY52706092025000002</t>
-  </si>
-  <si>
-    <t>27-10-2026 to 26-10-2036</t>
-  </si>
-  <si>
-    <t>POL-F&amp;A-Mar-25-13</t>
-  </si>
-  <si>
-    <t>TAMARIN SAVANNAH LTD</t>
-  </si>
-  <si>
-    <t>PY5274012025000001</t>
-  </si>
-  <si>
-    <t>03-03-2025 to 01-03-2026</t>
-  </si>
-  <si>
-    <t>POL-PL-Mar-25-14</t>
-  </si>
-  <si>
-    <t>PY52702032025000001</t>
-  </si>
-  <si>
-    <t>PUBLIC LIABILITY</t>
-  </si>
-  <si>
-    <t>POL-TPL-May-24-4</t>
-  </si>
-  <si>
-    <t>POL-TPL-May-24-4\E1</t>
-  </si>
-  <si>
-    <t>MARGEOT NICHOLAS GERARD MR</t>
-  </si>
-  <si>
-    <t>PY5270803202000010</t>
-  </si>
-  <si>
-    <t>12-03-2025 to 01-06-2025</t>
-  </si>
-  <si>
-    <t>MARINE THIRD PARTY LIABILITY</t>
-  </si>
-  <si>
-    <t>POL-DEF-Mar-25-1011</t>
-  </si>
-  <si>
-    <t>CREATIVE PROPERTIES LTD &amp;/OR SUBSEQUENT OWNERS</t>
-  </si>
-  <si>
-    <t>15-01-2026 to 14-01-2036</t>
-  </si>
-  <si>
-    <t>POL-CAR-TPL-Jul-23-1050</t>
-  </si>
-  <si>
-    <t>POL-CAR-TPL-Jul-23-1050\E1</t>
-  </si>
-  <si>
-    <t>DN52706012025000015</t>
-  </si>
-  <si>
-    <t>01-04-2025 to 31-03-2026</t>
-  </si>
-  <si>
-    <t>POL-CAR-TPL-Sep-23-1059\E2</t>
-  </si>
-  <si>
-    <t>31-05-2025 to 31-08-2025</t>
   </si>
   <si>
     <t>POL-CAR-TPL-Sep-23-1060\E2</t>
@@ -490,9 +490,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -589,17 +589,17 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="4" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="41" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1024,31 +1024,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5821F0DD-FA9D-42D0-B232-1CBACDE69859}">
   <dimension ref="A1:T46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="75" customWidth="1"/>
+    <col min="5" max="5" width="60.5703125" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" customWidth="1"/>
-    <col min="15" max="15" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" customWidth="1"/>
-    <col min="19" max="19" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.88671875" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" customWidth="1"/>
+    <col min="15" max="15" width="19" customWidth="1"/>
+    <col min="16" max="16" width="19.42578125" customWidth="1"/>
+    <col min="17" max="17" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26.5703125" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" customWidth="1"/>
+    <col min="20" max="20" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1070,7 +1070,7 @@
       <c r="S1" s="6"/>
       <c r="T1" s="4"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -1092,7 +1092,7 @@
       <c r="S2" s="6"/>
       <c r="T2" s="4"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1114,7 +1114,7 @@
       <c r="S3" s="6"/>
       <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1136,7 +1136,7 @@
       <c r="S4" s="6"/>
       <c r="T4" s="4"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1158,7 +1158,7 @@
       <c r="S5" s="6"/>
       <c r="T5" s="4"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1186,7 +1186,7 @@
       <c r="S6" s="6"/>
       <c r="T6" s="4"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20">
       <c r="A7" s="7" t="s">
         <v>0</v>
       </c>
@@ -1212,7 +1212,7 @@
       <c r="S7" s="6"/>
       <c r="T7" s="4"/>
     </row>
-    <row r="8" spans="1:20" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="46.5">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -1274,24 +1274,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="G9" s="5">
         <v>575575</v>
@@ -1327,16 +1327,16 @@
         <v>69068.740000000005</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S9" s="6">
         <v>45016.699270833298</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="A10" s="4" t="s">
         <v>21</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G10" s="5">
         <v>3371316.22</v>
@@ -1395,10 +1395,10 @@
         <v>45085.464502314797</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
@@ -1412,10 +1412,10 @@
         <v>33</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G11" s="5">
         <v>2633893.5</v>
@@ -1457,27 +1457,27 @@
         <v>45097.6734490741</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="F12" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G12" s="5">
         <v>913623.88</v>
@@ -1513,33 +1513,33 @@
         <v>137044</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S12" s="6">
         <v>45169.449409722198</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>42</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G13" s="5">
         <v>3292511.81</v>
@@ -1575,33 +1575,33 @@
         <v>444489.26</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S13" s="6">
         <v>45169.441087963001</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="A14" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G14" s="5">
         <v>3040785.96</v>
@@ -1637,33 +1637,33 @@
         <v>410506.19</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S14" s="6">
         <v>45169.441087963001</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G15" s="5">
         <v>5065402.8</v>
@@ -1699,33 +1699,33 @@
         <v>759810</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S15" s="6">
         <v>45169.441087963001</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="A16" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G16" s="5">
         <v>4887500</v>
@@ -1761,33 +1761,33 @@
         <v>659812.43999999994</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="S16" s="6">
         <v>45273.667754629598</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20">
       <c r="A17" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G17" s="5">
         <v>6684375</v>
@@ -1823,33 +1823,33 @@
         <v>902390.38</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="S17" s="6">
         <v>45427.585555555597</v>
       </c>
       <c r="T17" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20">
       <c r="A18" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G18" s="5">
         <v>504687.5</v>
@@ -1885,33 +1885,33 @@
         <v>60562.34</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="S18" s="6">
         <v>45246.394641203697</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G19" s="5">
         <v>3534850.77</v>
@@ -1947,33 +1947,33 @@
         <v>424182.41</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="S19" s="6">
         <v>45427.415810185201</v>
       </c>
       <c r="T19" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G20" s="5">
         <v>637261</v>
@@ -2009,33 +2009,33 @@
         <v>95589</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="S20" s="6">
         <v>45461.412997685198</v>
       </c>
       <c r="T20" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G21" s="5">
         <v>2812500</v>
@@ -2071,33 +2071,33 @@
         <v>337499.96</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="S21" s="6">
         <v>45471.414259259298</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G22" s="5">
         <v>18289.52</v>
@@ -2133,33 +2133,33 @@
         <v>1953.19</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="S22" s="6">
         <v>45609.353356481501</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="29.25">
       <c r="A23" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G23" s="5">
         <v>4192549.69</v>
@@ -2186,7 +2186,7 @@
         <v>-3371779</v>
       </c>
       <c r="O23" s="5">
-        <v>-2868673.0232883859</v>
+        <v>-2868673.0232883901</v>
       </c>
       <c r="P23" s="5">
         <v>125776.98</v>
@@ -2194,34 +2194,34 @@
       <c r="Q23" s="5">
         <v>503105.47</v>
       </c>
-      <c r="R23" s="4" t="s">
-        <v>74</v>
+      <c r="R23" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="S23" s="6">
         <v>45643.676030092603</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G24" s="5">
         <v>227953</v>
@@ -2257,33 +2257,33 @@
         <v>14818.14</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="S24" s="6">
         <v>45671.411539351902</v>
       </c>
       <c r="T24" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G25" s="5">
         <v>212500</v>
@@ -2319,33 +2319,33 @@
         <v>31875</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="S25" s="6">
         <v>45727.684722222199</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G26" s="5">
         <v>1250000</v>
@@ -2381,33 +2381,33 @@
         <v>187500</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="S26" s="6">
         <v>45727.684907407398</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
       <c r="A27" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G27" s="5">
         <v>27528.32</v>
@@ -2443,33 +2443,33 @@
         <v>4129</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="S27" s="6">
         <v>45765.515370370398</v>
       </c>
       <c r="T27" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>93</v>
-      </c>
       <c r="F28" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G28" s="5">
         <v>13600.07</v>
@@ -2505,33 +2505,33 @@
         <v>2040</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="S28" s="6">
         <v>45765.515740740702</v>
       </c>
       <c r="T28" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G29" s="5">
         <v>-1331.51</v>
@@ -2567,33 +2567,33 @@
         <v>-200</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="S29" s="6">
         <v>45741.338206018503</v>
       </c>
       <c r="T29" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
       <c r="A30" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G30" s="5">
         <v>1822112.7</v>
@@ -2629,33 +2629,33 @@
         <v>189829.14</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="S30" s="6">
         <v>45771.498530092598</v>
       </c>
       <c r="T30" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G31" s="5">
         <v>508330</v>
@@ -2691,33 +2691,33 @@
         <v>76250</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="S31" s="6">
         <v>45764.600312499999</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G32" s="5">
         <v>147227</v>
@@ -2753,33 +2753,33 @@
         <v>22084</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S32" s="6">
         <v>45765.5239351852</v>
       </c>
       <c r="T32" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
       <c r="A33" s="4" t="s">
         <v>21</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>110</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>111</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G33" s="5">
         <v>35000</v>
@@ -2815,16 +2815,16 @@
         <v>5250</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S33" s="6">
         <v>45765.5245601852</v>
       </c>
       <c r="T33" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
       <c r="A34" s="4" t="s">
         <v>21</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>114</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G34" s="5">
         <v>543413.35</v>
@@ -2883,10 +2883,10 @@
         <v>45789.573194444398</v>
       </c>
       <c r="T34" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
       <c r="A35" s="4" t="s">
         <v>21</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>117</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G35" s="5">
         <v>550687.05000000005</v>
@@ -2945,10 +2945,10 @@
         <v>45789.573622685202</v>
       </c>
       <c r="T35" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
       <c r="A36" s="4" t="s">
         <v>21</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G36" s="5">
         <v>517789.83</v>
@@ -3007,10 +3007,10 @@
         <v>45797.396967592598</v>
       </c>
       <c r="T36" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
       <c r="A37" s="4" t="s">
         <v>21</v>
       </c>
@@ -3021,13 +3021,13 @@
         <v>122</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G37" s="5">
         <v>436796.7</v>
@@ -3069,10 +3069,10 @@
         <v>45785.387384259302</v>
       </c>
       <c r="T37" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
       <c r="A38" s="4" t="s">
         <v>21</v>
       </c>
@@ -3083,13 +3083,13 @@
         <v>125</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G38" s="5">
         <v>598023.59</v>
@@ -3131,10 +3131,10 @@
         <v>45785.387847222199</v>
       </c>
       <c r="T38" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
       <c r="A39" s="4" t="s">
         <v>21</v>
       </c>
@@ -3145,13 +3145,13 @@
         <v>128</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G39" s="5">
         <v>757573.2</v>
@@ -3193,10 +3193,10 @@
         <v>45785.3882407407</v>
       </c>
       <c r="T39" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
       <c r="A40" s="4" t="s">
         <v>21</v>
       </c>
@@ -3207,13 +3207,13 @@
         <v>131</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G40" s="5">
         <v>505925.29</v>
@@ -3255,10 +3255,10 @@
         <v>45785.388854166697</v>
       </c>
       <c r="T40" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
       <c r="A41" s="4" t="s">
         <v>21</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>136</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G41" s="5">
         <v>115494</v>
@@ -3317,10 +3317,10 @@
         <v>45805.4219212963</v>
       </c>
       <c r="T41" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
       <c r="A42" s="4" t="s">
         <v>21</v>
       </c>
@@ -3337,7 +3337,7 @@
         <v>140</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G42" s="5">
         <v>519688</v>
@@ -3379,10 +3379,10 @@
         <v>45827.413680555597</v>
       </c>
       <c r="T42" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
       <c r="A43" s="4" t="s">
         <v>21</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G43" s="5">
         <v>1380224</v>
@@ -3441,10 +3441,10 @@
         <v>45831.488460648201</v>
       </c>
       <c r="T43" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
       <c r="A44" s="4" t="s">
         <v>21</v>
       </c>
@@ -3461,7 +3461,7 @@
         <v>147</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G44" s="5">
         <v>10628500</v>
@@ -3503,12 +3503,12 @@
         <v>45831.488692129598</v>
       </c>
       <c r="T44" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="15" thickBot="1">
+      <c r="A45" s="4" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O45" s="9">
         <f>SUM(O9:O44)</f>
-        <v>-48718960.46864213</v>
+        <v>-48718960.468642138</v>
       </c>
       <c r="P45" s="5"/>
       <c r="Q45" s="5"/>
@@ -3536,7 +3536,7 @@
       <c r="S45" s="6"/>
       <c r="T45" s="4"/>
     </row>
-    <row r="46" spans="1:20" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:20" ht="15" thickTop="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3544,6 +3544,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Status xmlns="411d9a0c-6800-433f-905c-961176f6889b">In Progress</Status>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E0666DBAD41D7242AB8886F9F2FC1A1D" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0831333aec8194218ced0aa379e26ffe">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="411d9a0c-6800-433f-905c-961176f6889b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cf8670012fa5c86a9e8fed8857f72cad" ns2:_="">
     <xsd:import namespace="411d9a0c-6800-433f-905c-961176f6889b"/>
@@ -3693,14 +3701,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Status xmlns="411d9a0c-6800-433f-905c-961176f6889b">In Progress</Status>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3711,24 +3711,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D1848C-BEE6-40D1-A539-2A6815A32067}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10799917-6F6D-454F-AFD9-9C4354F884EA}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12D1848C-BEE6-40D1-A539-2A6815A32067}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ad474b94-ba02-4e88-987e-f92536b7745b"/>
-    <ds:schemaRef ds:uri="5aff64d6-7803-4fb3-a6dc-2c7b0357e73e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7BAE7AB-32AF-47E0-B422-5910F8F24785}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7BAE7AB-32AF-47E0-B422-5910F8F24785}"/>
 </file>